--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5602.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5602.xlsx
@@ -1500,6 +1500,12 @@
           <t>5602-02-02-02-FG</t>
         </is>
       </c>
+      <c r="G17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.33</v>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>5602-02-02-02-FG</t>
@@ -1512,12 +1518,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-02-02-02 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-02-02-02 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-02-02-02 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-02-02-02 dims are NOT assumed; confirm before modelling | TAPDRILL2@BORE = Air-Way per-size tap drill -02 0.33 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -02 0.33 (A1)</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1537,6 +1543,12 @@
           <t>5602-06-06-06-FG</t>
         </is>
       </c>
+      <c r="G18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.57</v>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>5602-06-06-06-FG</t>
@@ -1549,12 +1561,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-06-06-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-06-06-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-06-06-06 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-06-06-06 dims are NOT assumed; confirm before modelling | TAPDRILL2@BORE = Air-Way per-size tap drill -06 0.57 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1574,6 +1586,12 @@
           <t>5602-12-12-12-FG</t>
         </is>
       </c>
+      <c r="G19" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.91</v>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>5602-12-12-12-FG</t>
@@ -1586,12 +1604,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-12-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-12-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-12-12-12 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-12-12-12 dims are NOT assumed; confirm before modelling | TAPDRILL2@BORE = Air-Way per-size tap drill -12 0.91 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1611,6 +1629,12 @@
           <t>5602-16-16-16-FG</t>
         </is>
       </c>
+      <c r="G20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.14</v>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>5602-16-16-16-FG</t>
@@ -1623,12 +1647,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-16-16-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-16-16-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-16-16-16 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-16-16-16 dims are NOT assumed; confirm before modelling | TAPDRILL2@BORE = Air-Way per-size tap drill -16 1.14 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -16 1.14 (A1)</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -1648,6 +1672,12 @@
           <t>5602-20-20-20-FG</t>
         </is>
       </c>
+      <c r="G21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.48</v>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>5602-20-20-20-FG</t>
@@ -1660,12 +1690,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-20-20-20 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-20-20-20 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-20-20-20 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-20-20-20 dims are NOT assumed; confirm before modelling | TAPDRILL2@BORE = Air-Way per-size tap drill -20 1.48 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -20 1.48 (A1)</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -1685,6 +1715,12 @@
           <t>5602-24-24-24-FG</t>
         </is>
       </c>
+      <c r="G22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.72</v>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>5602-24-24-24-FG</t>
@@ -1697,12 +1733,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-24-24-24 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-24-24-24 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-24-24-24 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-24-24-24 dims are NOT assumed; confirm before modelling | TAPDRILL2@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL3@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -1722,6 +1758,12 @@
           <t>5602-32-32-32-FG</t>
         </is>
       </c>
+      <c r="G23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.2</v>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>5602-32-32-32-FG</t>
@@ -1734,12 +1776,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-32-32-32 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-32-32-32 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-32-32-32 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-32-32-32 dims are NOT assumed; confirm before modelling | TAPDRILL2@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL3@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">

--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5602.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5602.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -553,6 +553,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1500,12 +1505,21 @@
           <t>5602-02-02-02-FG</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>0.78</v>
+      </c>
       <c r="G17" t="n">
         <v>0.33</v>
       </c>
       <c r="H17" t="n">
         <v>0.33</v>
       </c>
+      <c r="J17" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.405</v>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>5602-02-02-02-FG</t>
@@ -1518,12 +1532,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-02-02-02 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-02-02-02 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-02-02-02 dims are NOT assumed; confirm before modelling | TAPDRILL2@BORE = Air-Way per-size tap drill -02 0.33 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -02 0.33 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-02-02-02 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-02-02-02-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -02 0.33 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -02 0.33 (A1)</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1534,6 +1548,11 @@
       <c r="R17" t="inlineStr">
         <is>
           <t>5602-02-02-02-FG</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1562,21 @@
           <t>5602-06-06-06-FG</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>1.22</v>
+      </c>
       <c r="G18" t="n">
         <v>0.57</v>
       </c>
       <c r="H18" t="n">
         <v>0.57</v>
       </c>
+      <c r="J18" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.675</v>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>5602-06-06-06-FG</t>
@@ -1561,12 +1589,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-06-06-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-06-06-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-06-06-06 dims are NOT assumed; confirm before modelling | TAPDRILL2@BORE = Air-Way per-size tap drill -06 0.57 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-06-06-06 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-06-06-06-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -06 0.57 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1577,6 +1605,11 @@
       <c r="R18" t="inlineStr">
         <is>
           <t>5602-06-06-06-FG</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1619,21 @@
           <t>5602-12-12-12-FG</t>
         </is>
       </c>
+      <c r="B19" t="n">
+        <v>1.59</v>
+      </c>
       <c r="G19" t="n">
         <v>0.91</v>
       </c>
       <c r="H19" t="n">
         <v>0.91</v>
       </c>
+      <c r="J19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.05</v>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>5602-12-12-12-FG</t>
@@ -1604,12 +1646,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-12-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-12-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-12-12-12 dims are NOT assumed; confirm before modelling | TAPDRILL2@BORE = Air-Way per-size tap drill -12 0.91 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-12-12-12 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-12-12-12-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -12 0.91 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1620,6 +1662,11 @@
       <c r="R19" t="inlineStr">
         <is>
           <t>5602-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1629,12 +1676,21 @@
           <t>5602-16-16-16-FG</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>1.97</v>
+      </c>
       <c r="G20" t="n">
         <v>1.14</v>
       </c>
       <c r="H20" t="n">
         <v>1.14</v>
       </c>
+      <c r="J20" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.315</v>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>5602-16-16-16-FG</t>
@@ -1647,12 +1703,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-16-16-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-16-16-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-16-16-16 dims are NOT assumed; confirm before modelling | TAPDRILL2@BORE = Air-Way per-size tap drill -16 1.14 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -16 1.14 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-16-16-16 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-16-16-16-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -16 1.14 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -16 1.14 (A1)</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -1663,6 +1719,11 @@
       <c r="R20" t="inlineStr">
         <is>
           <t>5602-16-16-16-FG</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1733,21 @@
           <t>5602-20-20-20-FG</t>
         </is>
       </c>
+      <c r="B21" t="n">
+        <v>2.38</v>
+      </c>
       <c r="G21" t="n">
         <v>1.48</v>
       </c>
       <c r="H21" t="n">
         <v>1.48</v>
       </c>
+      <c r="J21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.66</v>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>5602-20-20-20-FG</t>
@@ -1690,12 +1760,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-20-20-20 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-20-20-20 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-20-20-20 dims are NOT assumed; confirm before modelling | TAPDRILL2@BORE = Air-Way per-size tap drill -20 1.48 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -20 1.48 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-20-20-20 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-20-20-20-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -20 1.48 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -20 1.48 (A1)</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -1706,6 +1776,11 @@
       <c r="R21" t="inlineStr">
         <is>
           <t>5602-20-20-20-FG</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1790,21 @@
           <t>5602-24-24-24-FG</t>
         </is>
       </c>
+      <c r="B22" t="n">
+        <v>2.64</v>
+      </c>
       <c r="G22" t="n">
         <v>1.72</v>
       </c>
       <c r="H22" t="n">
         <v>1.72</v>
       </c>
+      <c r="J22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.9</v>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>5602-24-24-24-FG</t>
@@ -1733,12 +1817,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-24-24-24 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-24-24-24 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-24-24-24 dims are NOT assumed; confirm before modelling | TAPDRILL2@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL3@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-24-24-24 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-24-24-24-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL3@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -1749,6 +1833,11 @@
       <c r="R22" t="inlineStr">
         <is>
           <t>5602-24-24-24-FG</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1847,21 @@
           <t>5602-32-32-32-FG</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
       <c r="G23" t="n">
         <v>2.2</v>
       </c>
       <c r="H23" t="n">
         <v>2.2</v>
       </c>
+      <c r="J23" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.375</v>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>5602-32-32-32-FG</t>
@@ -1776,12 +1874,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-32-32-32 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-32-32-32 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-32-32-32 dims are NOT assumed; confirm before modelling | TAPDRILL2@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL3@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-32-32-32 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-32-32-32-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL3@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -1792,6 +1890,11 @@
       <c r="R23" t="inlineStr">
         <is>
           <t>5602-32-32-32-FG</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5602.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5602.xlsx
@@ -1508,12 +1508,27 @@
       <c r="B17" t="n">
         <v>0.78</v>
       </c>
+      <c r="C17" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.188</v>
+      </c>
       <c r="G17" t="n">
         <v>0.33</v>
       </c>
       <c r="H17" t="n">
         <v>0.33</v>
       </c>
+      <c r="I17" t="n">
+        <v>0.405</v>
+      </c>
       <c r="J17" t="n">
         <v>0.405</v>
       </c>
@@ -1527,17 +1542,17 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-02-02-02 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, N1_2@DRIVE, N1_3@DRIVE, WY@REF, D@BORE, THDMAJ_A1@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-02-02-02 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-02-02-02 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-02-02-02-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -02 0.33 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -02 0.33 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-02-02-02 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-02-02-02-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD, N1_2@DRIVE=N1, N1_3@DRIVE=N2, WY@REF=Y, D@BORE=A1D, THDMAJ_A1@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -02 0.33 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -02 0.33 (A1)</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1565,12 +1580,27 @@
       <c r="B18" t="n">
         <v>1.22</v>
       </c>
+      <c r="C18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.406</v>
+      </c>
       <c r="G18" t="n">
         <v>0.57</v>
       </c>
       <c r="H18" t="n">
         <v>0.57</v>
       </c>
+      <c r="I18" t="n">
+        <v>0.675</v>
+      </c>
       <c r="J18" t="n">
         <v>0.675</v>
       </c>
@@ -1584,17 +1614,17 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-06-06-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, N1_2@DRIVE, N1_3@DRIVE, WY@REF, D@BORE, THDMAJ_A1@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-06-06-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-06-06-06 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-06-06-06-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -06 0.57 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-06-06-06 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-06-06-06-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD, N1_2@DRIVE=N1, N1_3@DRIVE=N2, WY@REF=Y, D@BORE=A1D, THDMAJ_A1@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -06 0.57 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1622,12 +1652,27 @@
       <c r="B19" t="n">
         <v>1.59</v>
       </c>
+      <c r="C19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.719</v>
+      </c>
       <c r="G19" t="n">
         <v>0.91</v>
       </c>
       <c r="H19" t="n">
         <v>0.91</v>
       </c>
+      <c r="I19" t="n">
+        <v>1.05</v>
+      </c>
       <c r="J19" t="n">
         <v>1.05</v>
       </c>
@@ -1641,17 +1686,17 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-12-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, N1_2@DRIVE, N1_3@DRIVE, WY@REF, D@BORE, THDMAJ_A1@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-12-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-12-12-12 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-12-12-12-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -12 0.91 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-12-12-12 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-12-12-12-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD, N1_2@DRIVE=N1, N1_3@DRIVE=N2, WY@REF=Y, D@BORE=A1D, THDMAJ_A1@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -12 0.91 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1679,12 +1724,27 @@
       <c r="B20" t="n">
         <v>1.97</v>
       </c>
+      <c r="C20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9379999999999999</v>
+      </c>
       <c r="G20" t="n">
         <v>1.14</v>
       </c>
       <c r="H20" t="n">
         <v>1.14</v>
       </c>
+      <c r="I20" t="n">
+        <v>1.315</v>
+      </c>
       <c r="J20" t="n">
         <v>1.315</v>
       </c>
@@ -1698,17 +1758,17 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-16-16-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, N1_2@DRIVE, N1_3@DRIVE, WY@REF, D@BORE, THDMAJ_A1@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-16-16-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-16-16-16 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-16-16-16-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -16 1.14 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -16 1.14 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-16-16-16 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-16-16-16-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD, N1_2@DRIVE=N1, N1_3@DRIVE=N2, WY@REF=Y, D@BORE=A1D, THDMAJ_A1@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -16 1.14 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -16 1.14 (A1)</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -1736,12 +1796,27 @@
       <c r="B21" t="n">
         <v>2.38</v>
       </c>
+      <c r="C21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.25</v>
+      </c>
       <c r="G21" t="n">
         <v>1.48</v>
       </c>
       <c r="H21" t="n">
         <v>1.48</v>
       </c>
+      <c r="I21" t="n">
+        <v>1.66</v>
+      </c>
       <c r="J21" t="n">
         <v>1.66</v>
       </c>
@@ -1755,17 +1830,17 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-20-20-20 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, N1_2@DRIVE, N1_3@DRIVE, WY@REF, D@BORE, THDMAJ_A1@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-20-20-20 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-20-20-20 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-20-20-20-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -20 1.48 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -20 1.48 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-20-20-20 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-20-20-20-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD, N1_2@DRIVE=N1, N1_3@DRIVE=N2, WY@REF=Y, D@BORE=A1D, THDMAJ_A1@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -20 1.48 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -20 1.48 (A1)</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -1793,12 +1868,27 @@
       <c r="B22" t="n">
         <v>2.64</v>
       </c>
+      <c r="C22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.562</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G22" t="n">
         <v>1.72</v>
       </c>
       <c r="H22" t="n">
         <v>1.72</v>
       </c>
+      <c r="I22" t="n">
+        <v>1.9</v>
+      </c>
       <c r="J22" t="n">
         <v>1.9</v>
       </c>
@@ -1812,17 +1902,17 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-24-24-24 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, N1_2@DRIVE, N1_3@DRIVE, WY@REF, D@BORE, THDMAJ_A1@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-24-24-24 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-24-24-24 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-24-24-24-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL3@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-24-24-24 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-24-24-24-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD, N1_2@DRIVE=N1, N1_3@DRIVE=N2, WY@REF=Y, D@BORE=A1D, THDMAJ_A1@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL3@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -1850,12 +1940,27 @@
       <c r="B23" t="n">
         <v>3</v>
       </c>
+      <c r="C23" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.812</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.938</v>
+      </c>
       <c r="G23" t="n">
         <v>2.2</v>
       </c>
       <c r="H23" t="n">
         <v>2.2</v>
       </c>
+      <c r="I23" t="n">
+        <v>2.375</v>
+      </c>
       <c r="J23" t="n">
         <v>2.375</v>
       </c>
@@ -1869,17 +1974,17 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-32-32-32 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [BRENNAN-CAD 2026-10-21: N@DRIVE, THDMAJ_A2@DRIVE, THDMAJ_A3@DRIVE, N1_2@DRIVE, N1_3@DRIVE, WY@REF, D@BORE, THDMAJ_A1@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5602-32-32-32 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-32-32-32 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-32-32-32-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL3@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5602-32-32-32 dims are NOT assumed; confirm before modelling | Brennan CAD record 5602-32-32-32-FG (PARTcommunity / CADENAS, N@DRIVE=N, THDMAJ_A2@DRIVE=A2THD, THDMAJ_A3@DRIVE=ATHD, N1_2@DRIVE=N1, N1_3@DRIVE=N2, WY@REF=Y, D@BORE=A1D, THDMAJ_A1@DRIVE=ATHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL2@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL3@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
